--- a/mode_docx_gen/pmi_mtz/part/lvttoc/ptoc2/PTOC2.xlsx
+++ b/mode_docx_gen/pmi_mtz/part/lvttoc/ptoc2/PTOC2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvttoc\ptoc2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_mtz\part\lvttoc\ptoc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D2BE6A-D764-4EE2-ACE6-E516E9D310D0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11820" yWindow="9540" windowWidth="17700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11820" yWindow="9540" windowWidth="17700" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -353,9 +352,6 @@
     <t>Контр_СВ</t>
   </si>
   <si>
-    <t>0 - Не предусмотрено, 1 - Блокировка ступени при включенном СВ, 3 -  Блокировка ступени при отключенном СВ</t>
-  </si>
-  <si>
     <t>Пуск ф.А</t>
   </si>
   <si>
@@ -446,12 +442,15 @@
   </si>
   <si>
     <t>Icoarse</t>
+  </si>
+  <si>
+    <t>0 - Не предусмотрено, 1 - Блокировка ступени при включенном СВ, 2 -  Блокировка ступени при отключенном СВ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -843,7 +842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -852,7 +851,7 @@
     <col min="3" max="3" width="42.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="63.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="82.140625" style="2" customWidth="1"/>
     <col min="7" max="12" width="9.140625" style="2"/>
     <col min="13" max="13" width="14.7109375" style="2" customWidth="1"/>
     <col min="14" max="26" width="9.140625" style="2"/>
@@ -953,7 +952,7 @@
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -961,7 +960,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>76</v>
@@ -1053,7 +1052,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>78</v>
@@ -1145,7 +1144,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
@@ -1220,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB4" s="3" t="s">
         <v>46</v>
@@ -1237,7 +1236,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
@@ -1312,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>50</v>
@@ -1329,16 +1328,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>31</v>
@@ -1421,16 +1420,16 @@
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>31</v>
@@ -1513,16 +1512,16 @@
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>31</v>
@@ -1605,16 +1604,16 @@
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>31</v>
@@ -1697,16 +1696,16 @@
         <v>30</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>31</v>
@@ -1789,16 +1788,16 @@
         <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>31</v>
@@ -1881,7 +1880,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>61</v>
@@ -1956,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>65</v>
@@ -1973,7 +1972,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>70</v>
@@ -2048,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB13" s="3" t="s">
         <v>72</v>
@@ -2065,7 +2064,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>73</v>
@@ -2157,7 +2156,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
@@ -2249,7 +2248,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>85</v>
@@ -2324,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>89</v>
@@ -2336,7 +2335,7 @@
         <v>31</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
@@ -2344,13 +2343,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>92</v>
@@ -2419,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>93</v>
@@ -2431,7 +2430,7 @@
         <v>31</v>
       </c>
       <c r="AE17" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
@@ -2439,7 +2438,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>100</v>
@@ -2451,7 +2450,7 @@
         <v>99</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -2514,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>101</v>
@@ -2531,7 +2530,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>66</v>
@@ -2606,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>69</v>
@@ -2623,7 +2622,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>103</v>
@@ -2635,7 +2634,7 @@
         <v>102</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -2698,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>106</v>
@@ -2709,13 +2708,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>105</v>
@@ -2784,10 +2783,10 @@
         <v>0</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -2795,13 +2794,13 @@
         <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>107</v>
@@ -2870,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
@@ -2881,7 +2880,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>108</v>
@@ -2890,10 +2889,10 @@
         <v>109</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>32</v>
@@ -2967,7 +2966,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>86</v>
@@ -3042,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>60</v>
@@ -3058,7 +3057,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
+  <sortState ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3067,7 +3066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3105,15 +3104,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6">
         <v>100</v>
